--- a/filer_1/32345794_maersk_a_s.xlsx
+++ b/filer_1/32345794_maersk_a_s.xlsx
@@ -5831,20 +5831,20 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>SUM(B5:B8)</f>
+        <f>IF(COUNT('res_raw'!$F$2,'res_raw'!$F$3,'res_raw'!$F$4,'res_raw'!$F$5)=0,'res_raw'!$F$6,SUM(B5:B8))</f>
         <v/>
       </c>
       <c r="C9" s="27">
-        <f>SUM(C5:C8)</f>
+        <f>IF(COUNT('res_raw'!$E$2,'res_raw'!$E$3,'res_raw'!$E$4,'res_raw'!$E$5)=0,'res_raw'!$E$6,SUM(C5:C8))</f>
         <v/>
       </c>
       <c r="D9" s="27">
-        <f>SUM(D5:D8)</f>
+        <f>IF(COUNT('res_raw'!$D$2,'res_raw'!$D$3,'res_raw'!$D$4,'res_raw'!$D$5)=0,'res_raw'!$D$6,SUM(D5:D8))</f>
         <v/>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Beregnet: Nettoomsætning + Andre driftsindt. − Vareforbrug − Andre ext. omk.</t>
+          <t>Beregnet: Nettoomsætning + Andre driftsindt. − Vareforbrug − Andre ext. omk. Er komponenterne ikke indberettet, vises rapporteret bruttoresultat (fsa:GrossResult) direkte.</t>
         </is>
       </c>
     </row>

--- a/filer_1/32345794_maersk_a_s.xlsx
+++ b/filer_1/32345794_maersk_a_s.xlsx
@@ -649,7 +649,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>apm (CVR None) — Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.USD)</t>
+          <t>apm — Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.USD)</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>apm (CVR None) — Resultatopgørelse &amp; nøgleoplysninger (t.USD)</t>
+          <t>apm — Resultatopgørelse &amp; nøgleoplysninger (t.USD)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -4772,7 +4772,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>apm (CVR None) — Balance (t.USD)</t>
+          <t>apm — Balance (t.USD)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -5576,7 +5576,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>apm (CVR None) — Pengestrømsopgørelse (t.USD)</t>
+          <t>apm — Pengestrømsopgørelse (t.USD)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -5692,7 +5692,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>apm (CVR None) — Regnskabs- og nøgletal — artsopdelt</t>
+          <t>apm — Regnskabs- og nøgletal — artsopdelt</t>
         </is>
       </c>
     </row>
@@ -5831,15 +5831,15 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>IF(COUNT('res_raw'!$F$2,'res_raw'!$F$3,'res_raw'!$F$4,'res_raw'!$F$5)=0,'res_raw'!$F$6,SUM(B5:B8))</f>
+        <f>IF(ABS((SUM(B5:B8))-'res_raw'!$F$6)&lt;=2,SUM(B5:B8),'res_raw'!$F$6)</f>
         <v/>
       </c>
       <c r="C9" s="27">
-        <f>IF(COUNT('res_raw'!$E$2,'res_raw'!$E$3,'res_raw'!$E$4,'res_raw'!$E$5)=0,'res_raw'!$E$6,SUM(C5:C8))</f>
+        <f>IF(ABS((SUM(C5:C8))-'res_raw'!$E$6)&lt;=2,SUM(C5:C8),'res_raw'!$E$6)</f>
         <v/>
       </c>
       <c r="D9" s="27">
-        <f>IF(COUNT('res_raw'!$D$2,'res_raw'!$D$3,'res_raw'!$D$4,'res_raw'!$D$5)=0,'res_raw'!$D$6,SUM(D5:D8))</f>
+        <f>IF(ABS((SUM(D5:D8))-'res_raw'!$D$6)&lt;=2,SUM(D5:D8),'res_raw'!$D$6)</f>
         <v/>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -5927,15 +5927,15 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(B9:B12)</f>
+        <f>IF(ABS((SUM(B9:B12))-'res_raw'!$F$11)&lt;=2,SUM(B9:B12),'res_raw'!$F$11)</f>
         <v/>
       </c>
       <c r="C13" s="27">
-        <f>SUM(C9:C12)</f>
+        <f>IF(ABS((SUM(C9:C12))-'res_raw'!$E$11)&lt;=2,SUM(C9:C12),'res_raw'!$E$11)</f>
         <v/>
       </c>
       <c r="D13" s="27">
-        <f>SUM(D9:D12)</f>
+        <f>IF(ABS((SUM(D9:D12))-'res_raw'!$D$11)&lt;=2,SUM(D9:D12),'res_raw'!$D$11)</f>
         <v/>
       </c>
       <c r="F13" s="28" t="inlineStr">
@@ -5999,15 +5999,15 @@
         </is>
       </c>
       <c r="B16" s="27">
-        <f>SUM(B13:B15)</f>
+        <f>IF(ABS((SUM(B13:B15))-'res_raw'!$F$16)&lt;=2,SUM(B13:B15),'res_raw'!$F$16)</f>
         <v/>
       </c>
       <c r="C16" s="27">
-        <f>SUM(C13:C15)</f>
+        <f>IF(ABS((SUM(C13:C15))-'res_raw'!$E$16)&lt;=2,SUM(C13:C15),'res_raw'!$E$16)</f>
         <v/>
       </c>
       <c r="D16" s="27">
-        <f>SUM(D13:D15)</f>
+        <f>IF(ABS((SUM(D13:D15))-'res_raw'!$D$16)&lt;=2,SUM(D13:D15),'res_raw'!$D$16)</f>
         <v/>
       </c>
       <c r="F16" s="28" t="inlineStr">
@@ -6918,7 +6918,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="33" t="inlineStr">
         <is>
-          <t>apm (CVR None) — Ukendte XBRL-felter — disse er noter og ikke en del af hoved-regnskabet</t>
+          <t>apm — Ukendte XBRL-felter — disse er noter og ikke en del af hoved-regnskabet</t>
         </is>
       </c>
     </row>

--- a/filer_1/32345794_maersk_a_s.xlsx
+++ b/filer_1/32345794_maersk_a_s.xlsx
@@ -4650,10 +4650,18 @@
         </is>
       </c>
       <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="17" t="n"/>
+      <c r="C15" s="17" t="n">
+        <v>-1528000</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>-353000</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>-273000</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>-896000</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
